--- a/WorkBot/main/data/order_archive/Johnston Paper/Johnston Paper_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Johnston Paper/Johnston Paper_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,279 +519,6 @@
       </c>
       <c r="E7" t="n">
         <v>129.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A12PETDM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lid Cater Tray 12"</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="E8" t="n">
-        <v>37.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A16PETDM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Lid Cater Tray 16"</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>32.62</v>
-      </c>
-      <c r="E9" t="n">
-        <v>65.23999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A18PETDM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Lid Cater Tray 18"</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>32.62</v>
-      </c>
-      <c r="E10" t="n">
-        <v>65.23999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>169500071</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tray Cater 12"</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="E11" t="n">
-        <v>48.18</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>169500072</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Tray Cater 16"</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>74.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>169500073</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tray Cater 18"</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>48.88</v>
-      </c>
-      <c r="E13" t="n">
-        <v>97.76000000000001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>E121S</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Foil Roll - 12"</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>42.12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>L6070</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Lid - Deli (64oz)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>88.09</v>
-      </c>
-      <c r="E15" t="n">
-        <v>88.09</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>10G108024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bag - Poly (10x8x24, 1mil)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="E16" t="n">
-        <v>42.75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LKC1624F</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Lid - Parfait (16/24oz)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>60.84</v>
-      </c>
-      <c r="E17" t="n">
-        <v>121.68</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T607646</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Container - Deli (64oz)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>133.01</v>
-      </c>
-      <c r="E18" t="n">
-        <v>133.01</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R801</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sandwich Picks</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="E19" t="n">
-        <v>24.32</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>K8</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Wrap - EZ Poly (8" x 10.75")</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="E20" t="n">
-        <v>323.65</v>
       </c>
     </row>
   </sheetData>
